--- a/data/trans_dic/P36BPD13_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P36BPD13_2023-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consumen preferentemente carne de pollo, pavo o conejo en vez de ternera, cerdo, hamburguesas o salchichas</t>
+          <t>Población que consumen preferentemente carne de pollo, pavo o conejo en vez de ternera, cerdo, hamburguesas o salchichas (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>81,4; 87,9</t>
+          <t>81,02; 87,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>88,23; 92,76</t>
+          <t>88,28; 92,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>85,48; 89,51</t>
+          <t>85,46; 89,5</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>79,11; 87,09</t>
+          <t>79,54; 86,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85,38; 90,99</t>
+          <t>85,61; 91,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83,0; 88,11</t>
+          <t>82,95; 87,75</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>81,55; 96,57</t>
+          <t>81,3; 95,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>82,95; 92,13</t>
+          <t>82,85; 91,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>83,17; 95,34</t>
+          <t>83,13; 95,46</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>82,1; 87,26</t>
+          <t>82,01; 87,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>85,36; 94,45</t>
+          <t>85,64; 95,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84,55; 91,0</t>
+          <t>84,54; 90,76</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>78,28; 86,0</t>
+          <t>77,94; 85,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>87,72; 92,69</t>
+          <t>87,5; 92,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85,29; 89,62</t>
+          <t>85,2; 89,63</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>83,12; 96,16</t>
+          <t>83,22; 95,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>84,69; 89,34</t>
+          <t>84,46; 89,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>85,42; 90,22</t>
+          <t>85,27; 90,21</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>83,76; 88,84</t>
+          <t>83,67; 88,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>87,65; 90,91</t>
+          <t>87,59; 90,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>86,06; 89,34</t>
+          <t>86,07; 88,99</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consumen preferentemente carne de pollo, pavo o conejo en vez de ternera, cerdo, hamburguesas o salchichas</t>
+          <t>Población que consumen preferentemente carne de pollo, pavo o conejo en vez de ternera, cerdo, hamburguesas o salchichas (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>408954; 441606</t>
+          <t>407011; 440414</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>391436; 411554</t>
+          <t>391678; 411354</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>808700; 846776</t>
+          <t>808456; 846664</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>354749; 390531</t>
+          <t>356697; 389389</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>323178; 344394</t>
+          <t>324055; 344585</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>686397; 728619</t>
+          <t>685969; 725658</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>541369; 641064</t>
+          <t>539696; 635318</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>135943; 150989</t>
+          <t>135789; 150467</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>688416; 789181</t>
+          <t>688066; 790193</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>845623; 898789</t>
+          <t>844671; 896942</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>832224; 920945</t>
+          <t>834995; 930748</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1695162; 1824615</t>
+          <t>1694968; 1819759</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>368657; 405021</t>
+          <t>367067; 403795</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>735027; 776724</t>
+          <t>733258; 778435</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1116439; 1173105</t>
+          <t>1115151; 1173139</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>199911; 231272</t>
+          <t>200149; 229971</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>640922; 676079</t>
+          <t>639216; 675449</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>851857; 899739</t>
+          <t>850358; 899681</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2810931; 2981709</t>
+          <t>2808061; 2970217</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3116725; 3232566</t>
+          <t>3114505; 3233774</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5948717; 6175010</t>
+          <t>5949331; 6150719</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36BPD13_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P36BPD13_2023-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,66%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>81,02; 87,67</t>
+          <t>82,3; 88,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>88,28; 92,72</t>
+          <t>87,6; 92,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>85,46; 89,5</t>
+          <t>85,58; 89,55</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,66%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>79,54; 86,83</t>
+          <t>79,5; 87,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85,61; 91,04</t>
+          <t>84,9; 90,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82,95; 87,75</t>
+          <t>83,07; 88,03</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>84,34%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>81,3; 95,7</t>
+          <t>78,98; 86,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>82,85; 91,81</t>
+          <t>82,54; 91,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>83,13; 95,46</t>
+          <t>81,38; 87,19</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>85,45%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>82,01; 87,08</t>
+          <t>81,86; 86,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>85,64; 95,46</t>
+          <t>84,13; 88,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84,54; 90,76</t>
+          <t>83,69; 87,1</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>86,38%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>77,94; 85,74</t>
+          <t>80,07; 87,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>87,5; 92,9</t>
+          <t>86,22; 90,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85,2; 89,63</t>
+          <t>84,47; 88,12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,64%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>83,22; 95,62</t>
+          <t>82,44; 94,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>84,46; 89,25</t>
+          <t>84,1; 88,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>85,27; 90,21</t>
+          <t>85,03; 89,74</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>86,22%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>83,67; 88,5</t>
+          <t>83,16; 86,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>87,59; 90,94</t>
+          <t>86,75; 88,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>86,07; 88,99</t>
+          <t>85,35; 87,05</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>426142</t>
+          <t>467801</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>402688</t>
+          <t>436674</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>828830</t>
+          <t>904475</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>407011; 440414</t>
+          <t>450786; 483515</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>391678; 411354</t>
+          <t>424023; 446765</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>808456; 846664</t>
+          <t>882994; 923972</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>373292</t>
+          <t>400405</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>334726</t>
+          <t>368047</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>708018</t>
+          <t>768452</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>356697; 389389</t>
+          <t>380478; 416363</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>324055; 344585</t>
+          <t>355337; 378307</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>685969; 725658</t>
+          <t>745254; 789773</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>591076</t>
+          <t>387299</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>144255</t>
+          <t>161778</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>735330</t>
+          <t>549077</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>539696; 635318</t>
+          <t>369047; 404713</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>135789; 150467</t>
+          <t>151666; 168511</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>688066; 790193</t>
+          <t>529796; 567601</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>873174</t>
+          <t>954086</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>869232</t>
+          <t>741568</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1742407</t>
+          <t>1695654</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>844671; 896942</t>
+          <t>921910; 978110</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>834995; 930748</t>
+          <t>722043; 759774</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1694968; 1819759</t>
+          <t>1660748; 1728453</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>388131</t>
+          <t>472413</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>753128</t>
+          <t>728761</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1141259</t>
+          <t>1201174</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>367067; 403795</t>
+          <t>451712; 490913</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>733258; 778435</t>
+          <t>712514; 744211</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1115151; 1173139</t>
+          <t>1174644; 1225386</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>218531</t>
+          <t>214339</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>658719</t>
+          <t>729041</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>877250</t>
+          <t>943380</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>200149; 229971</t>
+          <t>195569; 224760</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>639216; 675449</t>
+          <t>705741; 745912</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>850358; 899681</t>
+          <t>915234; 966022</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2870345</t>
+          <t>2896343</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3162747</t>
+          <t>3165868</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6033092</t>
+          <t>6062211</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2808061; 2970217</t>
+          <t>2845239; 2942092</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3114505; 3233774</t>
+          <t>3131794; 3204268</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5949331; 6150719</t>
+          <t>6001156; 6121061</t>
         </is>
       </c>
     </row>
